--- a/Examples/Example_4_mimo_model/data_exa4_independent.xlsx
+++ b/Examples/Example_4_mimo_model/data_exa4_independent.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ufbabr-my.sharepoint.com/personal/daniel_diniz_ufba_br/Documents/Projetos/MT-PEU/Examples/Example_4_mimo_model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ddssa\OneDrive - Universidade Federal da Bahia\Projetos\MT-PEU\Examples\Example_4_mimo_model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_AD4D361C20488DEA4E38A0E2445975DE5ADEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D31BA4A-A4EB-49F1-8023-9712AA13BD87}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F051DCF3-C3A4-474B-9F56-70EB468024E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="5">
   <si>
     <t>x1</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>ux2</t>
+  </si>
+  <si>
+    <t>0.01</t>
   </si>
 </sst>
 </file>
@@ -375,140 +378,140 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" t="s">
+        <v>4</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>1</v>
+      <c r="D3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="D4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="B5" t="s">
+        <v>4</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
-      <c r="D5">
-        <v>1</v>
+      <c r="D5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>10</v>
       </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="B6" t="s">
+        <v>4</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>1</v>
+      <c r="D6" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>15</v>
       </c>
-      <c r="B7">
-        <v>1</v>
+      <c r="B7" t="s">
+        <v>4</v>
       </c>
       <c r="C7">
         <v>15</v>
       </c>
-      <c r="D7">
-        <v>1</v>
+      <c r="D7" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>20</v>
       </c>
-      <c r="B8">
-        <v>1</v>
+      <c r="B8" t="s">
+        <v>4</v>
       </c>
       <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8">
-        <v>1</v>
+      <c r="D8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>30</v>
       </c>
-      <c r="B9">
-        <v>1</v>
+      <c r="B9" t="s">
+        <v>4</v>
       </c>
       <c r="C9">
         <v>30</v>
       </c>
-      <c r="D9">
-        <v>1</v>
+      <c r="D9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>40</v>
       </c>
-      <c r="B10">
-        <v>1</v>
+      <c r="B10" t="s">
+        <v>4</v>
       </c>
       <c r="C10">
         <v>40</v>
       </c>
-      <c r="D10">
-        <v>1</v>
+      <c r="D10" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>50</v>
       </c>
-      <c r="B11">
-        <v>1</v>
+      <c r="B11" t="s">
+        <v>4</v>
       </c>
       <c r="C11">
         <v>50</v>
       </c>
-      <c r="D11">
-        <v>1</v>
+      <c r="D11" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
